--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104715_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104715_W29.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.933</v>
+        <v>10.2785</v>
       </c>
       <c r="E2" t="n">
-        <v>8.183</v>
+        <v>8.228999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>1.75</v>
+        <v>2.0495</v>
       </c>
       <c r="G2" t="n">
-        <v>6.24</v>
+        <v>6.2226</v>
       </c>
       <c r="H2" t="n">
-        <v>1.2383</v>
+        <v>1.2252</v>
       </c>
       <c r="I2" t="n">
-        <v>5.0017</v>
+        <v>4.9974</v>
       </c>
       <c r="J2" t="n">
-        <v>6.3067</v>
+        <v>6.2784</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5532</v>
+        <v>2.5328</v>
       </c>
       <c r="L2" t="n">
-        <v>3.7534</v>
+        <v>3.7456</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-0.0558</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3149</v>
+        <v>-1.3077</v>
       </c>
       <c r="O2" t="n">
-        <v>1.2483</v>
+        <v>1.2518</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>0.055</v>
+        <v>0.4261</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7829</v>
+        <v>0.8706</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7278</v>
+        <v>-0.4444</v>
       </c>
       <c r="V2" t="n">
-        <v>3.6379</v>
+        <v>3.6298</v>
       </c>
       <c r="W2" t="n">
-        <v>3.5926</v>
+        <v>3.584</v>
       </c>
       <c r="X2" t="n">
-        <v>0.0454</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="3">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3959</v>
+        <v>3.9386</v>
       </c>
       <c r="E3" t="n">
-        <v>3.501</v>
+        <v>4.3314</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.1051</v>
+        <v>-0.3928</v>
       </c>
       <c r="G3" t="n">
-        <v>3.3718</v>
+        <v>3.3723</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.6259</v>
+        <v>-0.621</v>
       </c>
       <c r="I3" t="n">
-        <v>3.9978</v>
+        <v>3.9933</v>
       </c>
       <c r="J3" t="n">
-        <v>4.5025</v>
+        <v>4.49</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7491</v>
+        <v>0.7444</v>
       </c>
       <c r="L3" t="n">
-        <v>3.7534</v>
+        <v>3.7456</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.1307</v>
+        <v>-1.1177</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.375</v>
+        <v>-1.3654</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2443</v>
+        <v>0.2477</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5113</v>
+        <v>0.0256</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9338</v>
+        <v>-0.0887</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4225</v>
+        <v>0.1143</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5094</v>
+        <v>-1.508</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.6688</v>
+        <v>-1.6658</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3757</v>
+        <v>1.9612</v>
       </c>
       <c r="E4" t="n">
-        <v>4.9591</v>
+        <v>4.4374</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.5835</v>
+        <v>-2.4762</v>
       </c>
       <c r="G4" t="n">
-        <v>1.5055</v>
+        <v>1.5031</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5321</v>
+        <v>2.5278</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.0266</v>
+        <v>-1.0247</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6262</v>
+        <v>4.6133</v>
       </c>
       <c r="K4" t="n">
-        <v>4.1475</v>
+        <v>4.1368</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4787</v>
+        <v>0.4764</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.1207</v>
+        <v>-3.1102</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.6154</v>
+        <v>-1.6091</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5052</v>
+        <v>-1.5011</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.5903</v>
+        <v>-1.5934</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9966</v>
+        <v>0.5887</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2183</v>
+        <v>0.7151</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2216</v>
+        <v>-0.1264</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7823</v>
+        <v>0.7799</v>
       </c>
       <c r="W4" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0772</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="5">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2426</v>
+        <v>1.2136</v>
       </c>
       <c r="E5" t="n">
-        <v>2.7694</v>
+        <v>1.8815</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.5268</v>
+        <v>-0.6679</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2812</v>
+        <v>-0.2792</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8686</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1497</v>
+        <v>-1.1467</v>
       </c>
       <c r="J5" t="n">
-        <v>2.1633</v>
+        <v>2.1559</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4922</v>
+        <v>1.4856</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6711</v>
+        <v>0.6703</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4444</v>
+        <v>-2.4351</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6237</v>
+        <v>-0.6182</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8208</v>
+        <v>-1.8169</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5241</v>
+        <v>0.4912</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0605</v>
+        <v>0.1808</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4637</v>
+        <v>0.3104</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7724</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2373</v>
+        <v>0.3674</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7284</v>
+        <v>-0.1678</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4911</v>
+        <v>0.5352</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.7765</v>
+        <v>-1.7706</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8964</v>
+        <v>-0.8935</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8801</v>
+        <v>-0.877</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1928</v>
+        <v>0.1924</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1555</v>
+        <v>0.1551</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9693</v>
+        <v>-1.9629</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0519</v>
+        <v>-1.0487</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6418</v>
+        <v>-0.0476</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.1326</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0523</v>
+        <v>0.0849</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8178</v>
+        <v>0.8198</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8178</v>
+        <v>0.8198</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7192</v>
+        <v>-0.6604</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8776</v>
+        <v>-0.5851</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1584</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.5592</v>
+        <v>-3.5546</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.3901</v>
+        <v>-3.3864</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.1691</v>
+        <v>-0.1682</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.9269</v>
+        <v>-1.9326</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.399</v>
+        <v>-1.4037</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5279</v>
+        <v>-0.529</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6323</v>
+        <v>-1.6219</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.9911</v>
+        <v>-1.9827</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3588</v>
+        <v>0.3608</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1805</v>
+        <v>0.2369</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2526</v>
+        <v>0.5571</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0722</v>
+        <v>-0.3202</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0692</v>
+        <v>1.0639</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0238</v>
+        <v>1.018</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0454</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9294</v>
+        <v>-1.3805</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.4922</v>
+        <v>-0.7707000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4372</v>
+        <v>-0.6098</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.513</v>
+        <v>-1.5129</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.8438</v>
+        <v>-2.8432</v>
       </c>
       <c r="I8" t="n">
-        <v>1.3308</v>
+        <v>1.3302</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9749</v>
+        <v>-0.9817</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4162</v>
+        <v>-1.4209</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4414</v>
+        <v>0.4392</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5382</v>
+        <v>-0.5312</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4276</v>
+        <v>-1.4223</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8894</v>
+        <v>0.8911</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0745</v>
+        <v>0.4692</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5173</v>
+        <v>0.2111</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4428</v>
+        <v>0.2581</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="9">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1092</v>
+        <v>-2.0765</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8237</v>
+        <v>-0.8249</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2855</v>
+        <v>-1.2516</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8116</v>
+        <v>-0.8117</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5966</v>
+        <v>-0.5972</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7543</v>
+        <v>-0.7552</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7543</v>
+        <v>-0.7552</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.0573</v>
+        <v>-0.0565</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.215</v>
+        <v>-0.2144</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,22 +1156,22 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2064</v>
+        <v>-0.1754</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0694</v>
+        <v>-0.0697</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.609</v>
+        <v>-2.6153</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8418</v>
+        <v>-1.1426</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7673</v>
+        <v>-1.4726</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5165999999999999</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7597</v>
+        <v>-0.7533</v>
       </c>
       <c r="I10" t="n">
-        <v>1.2762</v>
+        <v>1.275</v>
       </c>
       <c r="J10" t="n">
-        <v>2.5911</v>
+        <v>2.5858</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3975</v>
+        <v>0.3964</v>
       </c>
       <c r="L10" t="n">
-        <v>2.1936</v>
+        <v>2.1893</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0745</v>
+        <v>-2.064</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1571</v>
+        <v>-1.1497</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9174</v>
+        <v>-0.9143</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.9534</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8622</v>
+        <v>-3.8697</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1721</v>
+        <v>-0.1778</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4294</v>
+        <v>0.1414</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6015</v>
+        <v>-0.3191</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.2307</v>
+        <v>-2.8318</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1482</v>
+        <v>0.3165</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.3788</v>
+        <v>-3.1483</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2745</v>
+        <v>-1.2744</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.8025</v>
+        <v>-1.8034</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5279</v>
+        <v>0.529</v>
       </c>
       <c r="J11" t="n">
-        <v>2.0039</v>
+        <v>1.9937</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3448</v>
+        <v>-0.3522</v>
       </c>
       <c r="L11" t="n">
-        <v>2.3487</v>
+        <v>2.3459</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2784</v>
+        <v>-3.2681</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.4577</v>
+        <v>-1.4511</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8208</v>
+        <v>-1.8169</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7755</v>
+        <v>-0.3706</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4479</v>
+        <v>-0.2627</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3276</v>
+        <v>-0.1078</v>
       </c>
       <c r="V11" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W11" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. ORIOLA</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.5859</v>
+        <v>-3.305</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9034</v>
+        <v>-4.6482</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.6825</v>
+        <v>1.3432</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.33</v>
+        <v>-3.0418</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.0264</v>
+        <v>1.9105</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3036</v>
+        <v>-4.9523</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8784</v>
+        <v>-2.2252</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.1766</v>
+        <v>2.5576</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2983</v>
+        <v>-4.7828</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4516</v>
+        <v>-0.8166</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1502</v>
+        <v>-0.6471</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6018</v>
+        <v>-0.1695</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.4544</v>
+        <v>-2.7316</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>2.2763</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6316000000000001</v>
+        <v>0.1462</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4294</v>
+        <v>0.3085</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2022</v>
+        <v>-0.1623</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3419</v>
+        <v>0.0458</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3419</v>
+        <v>0.0458</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>P. ORIOLA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1633</v>
+        <v>-4.1449</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.116</v>
+        <v>-2.0769</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9527</v>
+        <v>-2.068</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.0325</v>
+        <v>-2.3228</v>
       </c>
       <c r="H13" t="n">
-        <v>1.916</v>
+        <v>-2.0223</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.9484</v>
+        <v>-0.3005</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.207</v>
+        <v>-1.8814</v>
       </c>
       <c r="K13" t="n">
-        <v>2.5697</v>
+        <v>-2.1793</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.7767</v>
+        <v>0.2979</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.8255</v>
+        <v>-0.4414</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6536999999999999</v>
+        <v>0.157</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.1718</v>
+        <v>-0.5984</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7262</v>
+        <v>-0.4553</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2719</v>
+        <v>0.9105</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7218</v>
+        <v>0.0593</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1828</v>
+        <v>0.2598</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.539</v>
+        <v>-0.2005</v>
       </c>
       <c r="V13" t="n">
-        <v>0.0454</v>
+        <v>-2.3367</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0454</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.6367999999999987</v>
+        <v>0.7449000000000012</v>
       </c>
       <c r="E14" t="n">
-        <v>7.777600000000001</v>
+        <v>8.9796</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.4145</v>
+        <v>-8.234599999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.9446</v>
+        <v>-2.948300000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>-6.386400000000002</v>
+        <v>-6.3894</v>
       </c>
       <c r="I14" t="n">
-        <v>3.441900000000001</v>
+        <v>3.441100000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>14.645</v>
+        <v>14.5334</v>
       </c>
       <c r="K14" t="n">
-        <v>5.973800000000001</v>
+        <v>5.897399999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>8.671299999999999</v>
+        <v>8.6356</v>
       </c>
       <c r="M14" t="n">
-        <v>-17.5895</v>
+        <v>-17.4814</v>
       </c>
       <c r="N14" t="n">
-        <v>-12.3601</v>
+        <v>-12.2871</v>
       </c>
       <c r="O14" t="n">
-        <v>-5.2294</v>
+        <v>-5.1944</v>
       </c>
       <c r="P14" t="n">
-        <v>8.881784197001252e-16</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.7673</v>
+        <v>-14.7959</v>
       </c>
       <c r="R14" t="n">
-        <v>14.7672</v>
+        <v>14.7959</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2844000000000002</v>
+        <v>1.6718</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3278</v>
+        <v>2.6907</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0432</v>
+        <v>-1.0187</v>
       </c>
       <c r="V14" t="n">
-        <v>2.023</v>
+        <v>2.0212</v>
       </c>
       <c r="W14" t="n">
-        <v>6.572100000000001</v>
+        <v>6.5518</v>
       </c>
       <c r="X14" t="n">
-        <v>-4.5491</v>
+        <v>-4.5307</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. COSTELLO</t>
+          <t>D. THOMPSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.9996</v>
+        <v>3.4254</v>
       </c>
       <c r="E15" t="n">
-        <v>4.4635</v>
+        <v>3.2335</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4639</v>
+        <v>0.1919</v>
       </c>
       <c r="G15" t="n">
-        <v>1.0206</v>
+        <v>1.9455</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7483</v>
+        <v>-0.552</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2723</v>
+        <v>2.4975</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9946</v>
+        <v>2.833</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5899</v>
+        <v>-0.0485</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4047</v>
+        <v>2.8815</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.974</v>
+        <v>-0.8875999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8416</v>
+        <v>-0.5036</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1324</v>
+        <v>-0.384</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5903</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8434</v>
+        <v>0.4588</v>
       </c>
       <c r="T15" t="n">
-        <v>1.8998</v>
+        <v>-0.0955</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0564</v>
+        <v>0.5543</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.3188</v>
+        <v>1.4764</v>
       </c>
       <c r="W15" t="n">
-        <v>0.705</v>
+        <v>1.6342</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0238</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.55</v>
+        <v>3.0342</v>
       </c>
       <c r="E16" t="n">
-        <v>4.3286</v>
+        <v>4.1974</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7786</v>
+        <v>-1.1632</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4377</v>
+        <v>3.4385</v>
       </c>
       <c r="H16" t="n">
-        <v>1.565</v>
+        <v>1.5676</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8727</v>
+        <v>1.8708</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9355</v>
+        <v>3.926</v>
       </c>
       <c r="K16" t="n">
-        <v>2.2638</v>
+        <v>2.258</v>
       </c>
       <c r="L16" t="n">
-        <v>1.6717</v>
+        <v>1.668</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4978</v>
+        <v>-0.4876</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6988</v>
+        <v>-0.6904</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2011</v>
+        <v>0.2028</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3868</v>
+        <v>0.09180000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2336</v>
+        <v>0.1136</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6205000000000001</v>
+        <v>-0.0218</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7963</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. THOMPSON</t>
+          <t>M. COSTELLO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3175</v>
+        <v>2.1649</v>
       </c>
       <c r="E17" t="n">
-        <v>2.8972</v>
+        <v>3.3833</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.5796</v>
+        <v>-1.2184</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9464</v>
+        <v>1.0229</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5568</v>
+        <v>0.7519</v>
       </c>
       <c r="I17" t="n">
-        <v>2.5032</v>
+        <v>0.271</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8441</v>
+        <v>2.9855</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0458</v>
+        <v>1.5858</v>
       </c>
       <c r="L17" t="n">
-        <v>2.89</v>
+        <v>1.3997</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.8978</v>
+        <v>-1.9626</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.511</v>
+        <v>-0.8339</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3868</v>
+        <v>-1.1287</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6816</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6519</v>
+        <v>1.0023</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4479</v>
+        <v>0.8335</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.204</v>
+        <v>0.1688</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4775</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6369</v>
+        <v>0.7025</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1594</v>
+        <v>-1.018</v>
       </c>
     </row>
     <row r="18">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1963</v>
+        <v>1.6082</v>
       </c>
       <c r="E18" t="n">
-        <v>0.35</v>
+        <v>0.8128</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.7953</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6329</v>
+        <v>-1.6345</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4372</v>
+        <v>-0.4417</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1957</v>
+        <v>-1.1929</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3248</v>
+        <v>-0.3322</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3621</v>
+        <v>-0.3695</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.3081</v>
+        <v>-1.3023</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0752</v>
+        <v>-0.0722</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2329</v>
+        <v>-1.2301</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0796</v>
+        <v>0.3322</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4164</v>
+        <v>0.0556</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3369</v>
+        <v>0.2766</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. MOORE</t>
+          <t>B. BADIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8313</v>
+        <v>1.244</v>
       </c>
       <c r="E19" t="n">
-        <v>3.1352</v>
+        <v>3.1598</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.304</v>
+        <v>-1.9158</v>
       </c>
       <c r="G19" t="n">
-        <v>0.328</v>
+        <v>4.759</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4711</v>
+        <v>3.1283</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1431</v>
+        <v>1.6308</v>
       </c>
       <c r="J19" t="n">
-        <v>3.0908</v>
+        <v>4.4846</v>
       </c>
       <c r="K19" t="n">
-        <v>1.786</v>
+        <v>3.316</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3048</v>
+        <v>1.1686</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7629</v>
+        <v>0.2745</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3149</v>
+        <v>-0.1877</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.448</v>
+        <v>0.4622</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3631</v>
+        <v>0.6829</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8218</v>
+        <v>-0.1555</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1803</v>
+        <v>-0.5508</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3586</v>
+        <v>0.3953</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5456</v>
+        <v>-4.0424</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5456</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. KEY</t>
+          <t>O. MOORE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4341</v>
+        <v>0.4864</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.348</v>
+        <v>2.6496</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7821</v>
+        <v>-2.1632</v>
       </c>
       <c r="G20" t="n">
-        <v>1.5992</v>
+        <v>0.3297</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9534</v>
+        <v>0.471</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6458</v>
+        <v>-0.1413</v>
       </c>
       <c r="J20" t="n">
-        <v>2.2959</v>
+        <v>3.0819</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9911</v>
+        <v>1.7786</v>
       </c>
       <c r="L20" t="n">
-        <v>1.3048</v>
+        <v>1.3033</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6967</v>
+        <v>-2.7522</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.0376</v>
+        <v>-1.3077</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6591</v>
+        <v>-1.4446</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.0447</v>
+        <v>0.2276</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4078</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8796</v>
+        <v>0.4738</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7639</v>
+        <v>0.7058</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1157</v>
+        <v>-0.232</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. BADIO</t>
+          <t>I. NOGUES</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2949</v>
+        <v>0.0784</v>
       </c>
       <c r="E21" t="n">
-        <v>2.8304</v>
+        <v>-0.7907</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5355</v>
+        <v>0.8691</v>
       </c>
       <c r="G21" t="n">
-        <v>4.769</v>
+        <v>-0.2537</v>
       </c>
       <c r="H21" t="n">
-        <v>3.1347</v>
+        <v>0.2958</v>
       </c>
       <c r="I21" t="n">
-        <v>1.6344</v>
+        <v>-0.5496</v>
       </c>
       <c r="J21" t="n">
-        <v>4.5051</v>
+        <v>0.3475</v>
       </c>
       <c r="K21" t="n">
-        <v>3.3301</v>
+        <v>0.3103</v>
       </c>
       <c r="L21" t="n">
-        <v>1.175</v>
+        <v>0.0372</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2639</v>
+        <v>-0.6012</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1954</v>
+        <v>-0.0144</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4594</v>
+        <v>-0.5868</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6816</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6816</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1095</v>
+        <v>0.1046</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9023</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2073</v>
+        <v>0.1046</v>
       </c>
       <c r="V21" t="n">
-        <v>-4.0462</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7724</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-3.2738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. NOGUES</t>
+          <t>B. KEY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0143</v>
+        <v>-0.2933</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7876</v>
+        <v>-1.1932</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8018999999999999</v>
+        <v>0.8999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2545</v>
+        <v>1.6043</v>
       </c>
       <c r="H22" t="n">
-        <v>0.296</v>
+        <v>0.956</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.5506</v>
+        <v>0.6484</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3483</v>
+        <v>2.289</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3111</v>
+        <v>0.9858</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>1.3033</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6029</v>
+        <v>-0.6847</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.015</v>
+        <v>-0.0298</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5878</v>
+        <v>-0.6549</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2272</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1359</v>
+        <v>-3.4145</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0416</v>
+        <v>0.1511</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-0.0678</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0416</v>
+        <v>0.2189</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9798</v>
+        <v>-0.6167</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3027</v>
+        <v>-1.075</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3229</v>
+        <v>0.4583</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.3774</v>
+        <v>-0.3757</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1165</v>
+        <v>-0.1151</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.261</v>
+        <v>-0.2607</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3427</v>
+        <v>-0.3472</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3344</v>
+        <v>0.3308</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6771</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0348</v>
+        <v>-0.0285</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4508</v>
+        <v>-0.4458</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4161</v>
+        <v>0.4173</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6709000000000001</v>
+        <v>-0.3077</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.347</v>
+        <v>-0.1116</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3239</v>
+        <v>-0.1961</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.613</v>
+        <v>-0.6162</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.613</v>
+        <v>-0.6162</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. REUVERS</t>
+          <t>S. DE LARREA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.9455</v>
+        <v>-1.1358</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.1086</v>
+        <v>-0.7342</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.8369</v>
+        <v>-0.4016</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1992</v>
+        <v>-1.971</v>
       </c>
       <c r="H24" t="n">
-        <v>0.8038999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.0031</v>
+        <v>-2.0288</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6854</v>
+        <v>0.4205</v>
       </c>
       <c r="K24" t="n">
-        <v>1.4577</v>
+        <v>0.7337</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.143</v>
+        <v>-0.3132</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5139</v>
+        <v>-2.3915</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8601</v>
+        <v>-1.7155</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6816</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4544</v>
+        <v>2.2763</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1559</v>
+        <v>-0.2543</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3785</v>
+        <v>0.0322</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2226</v>
+        <v>-0.2865</v>
       </c>
       <c r="V24" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W24" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. DE LARREA</t>
+          <t>N. REUVERS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,64 +2359,64 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.1899</v>
+        <v>-1.2456</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.422</v>
+        <v>-0.7689</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7679</v>
+        <v>-0.4767</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.9704</v>
+        <v>-2.1992</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0601</v>
+        <v>0.8041</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.0305</v>
+        <v>-3.0033</v>
       </c>
       <c r="J25" t="n">
-        <v>0.4337</v>
+        <v>-0.6944</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7439</v>
+        <v>1.4511</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.3102</v>
+        <v>-2.1455</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.404</v>
+        <v>-1.5048</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.6838</v>
+        <v>-0.6471</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.7203</v>
+        <v>-0.8578</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>2.2719</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3108</v>
+        <v>0.547</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6751</v>
+        <v>-0.0258</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6357</v>
+        <v>0.5729</v>
       </c>
       <c r="V25" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W25" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.8858</v>
+        <v>-4.9424</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.5301</v>
+        <v>-3.5504</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.3556</v>
+        <v>-1.3921</v>
       </c>
       <c r="G26" t="n">
-        <v>-3.7219</v>
+        <v>-3.7174</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.5357</v>
+        <v>-0.5343</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.1862</v>
+        <v>-3.1831</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.5057</v>
+        <v>-1.5128</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.0398</v>
+        <v>-0.0452</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.466</v>
+        <v>-1.4676</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.2162</v>
+        <v>-2.2047</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.4959</v>
+        <v>-0.4891</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P26" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S26" t="n">
-        <v>0.4946</v>
+        <v>0.4367</v>
       </c>
       <c r="T26" t="n">
-        <v>0.1328</v>
+        <v>0.1297</v>
       </c>
       <c r="U26" t="n">
-        <v>0.3619</v>
+        <v>0.3071</v>
       </c>
       <c r="V26" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6370000000000005</v>
+        <v>3.8077</v>
       </c>
       <c r="E27" t="n">
-        <v>9.5059</v>
+        <v>9.324</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.8688</v>
+        <v>-5.5165</v>
       </c>
       <c r="G27" t="n">
-        <v>2.944600000000001</v>
+        <v>2.948400000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>6.386299999999999</v>
+        <v>6.3894</v>
       </c>
       <c r="I27" t="n">
-        <v>-3.4418</v>
+        <v>-3.4412</v>
       </c>
       <c r="J27" t="n">
-        <v>17.5894</v>
+        <v>17.4814</v>
       </c>
       <c r="K27" t="n">
-        <v>12.3603</v>
+        <v>12.2869</v>
       </c>
       <c r="L27" t="n">
-        <v>5.2293</v>
+        <v>5.1946</v>
       </c>
       <c r="M27" t="n">
-        <v>-14.6452</v>
+        <v>-14.5332</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.973699999999999</v>
+        <v>-5.8976</v>
       </c>
       <c r="O27" t="n">
-        <v>-8.671099999999999</v>
+        <v>-8.6356</v>
       </c>
       <c r="P27" t="n">
         <v>-4.440892098500626e-16</v>
       </c>
       <c r="Q27" t="n">
-        <v>-14.767</v>
+        <v>-14.7963</v>
       </c>
       <c r="R27" t="n">
-        <v>14.7672</v>
+        <v>14.7962</v>
       </c>
       <c r="S27" t="n">
-        <v>-0.2844</v>
+        <v>2.8808</v>
       </c>
       <c r="T27" t="n">
-        <v>1.0432</v>
+        <v>1.0189</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.3277</v>
+        <v>1.8621</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.022899999999999</v>
+        <v>-2.021099999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>5.640499999999999</v>
+        <v>5.6201</v>
       </c>
       <c r="X27" t="n">
-        <v>-7.6633</v>
+        <v>-7.6412</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104715_W29.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104715_W29.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.0458</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6658</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0.8198</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.0458</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.0458</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-4.5307</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.018</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104715_W29.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-7.6412</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
